--- a/results/mcolon/20260607_sci_cilia_gene14_imaging_qc/source_plate_metadata_excels/20260414_b9d2_14hpf_plate02_well_metadata.xlsx
+++ b/results/mcolon/20260607_sci_cilia_gene14_imaging_qc/source_plate_metadata_excels/20260414_b9d2_14hpf_plate02_well_metadata.xlsx
@@ -1,21 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/marazzanocolon/Downloads/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54EEF29-D870-7340-888C-4D2379AA1699}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17340" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="notes" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="genotype" sheetId="2" r:id="rId6"/>
-    <sheet state="visible" name="sequenced" sheetId="3" r:id="rId7"/>
-    <sheet state="visible" name="strain" sheetId="4" r:id="rId8"/>
-    <sheet state="visible" name="chem_perturbation" sheetId="5" r:id="rId9"/>
-    <sheet state="visible" name="start_age_hpf" sheetId="6" r:id="rId10"/>
-    <sheet state="visible" name="qc" sheetId="7" r:id="rId11"/>
-    <sheet state="visible" name="temperature" sheetId="8" r:id="rId12"/>
-    <sheet state="visible" name="image_to_hash_map" sheetId="9" r:id="rId13"/>
-    <sheet state="visible" name="hash_plate_num" sheetId="10" r:id="rId14"/>
+    <sheet name="notes" sheetId="1" r:id="rId1"/>
+    <sheet name="genotype" sheetId="2" r:id="rId2"/>
+    <sheet name="sequenced" sheetId="3" r:id="rId3"/>
+    <sheet name="strain" sheetId="4" r:id="rId4"/>
+    <sheet name="chem_perturbation" sheetId="5" r:id="rId5"/>
+    <sheet name="start_age_hpf" sheetId="6" r:id="rId6"/>
+    <sheet name="qc" sheetId="7" r:id="rId7"/>
+    <sheet name="temperature" sheetId="8" r:id="rId8"/>
+    <sheet name="image_to_hash_map" sheetId="9" r:id="rId9"/>
+    <sheet name="hash_plate_num" sheetId="10" r:id="rId10"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -64,29 +85,32 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="5">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12.0"/>
+      <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -97,7 +121,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -113,7 +137,13 @@
     </fill>
   </fills>
   <borders count="2">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left style="thin">
         <color rgb="FF000000"/>
@@ -127,140 +157,82 @@
       <bottom style="thin">
         <color rgb="FF000000"/>
       </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
-      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFCCCCCC"/>
+          <bgColor rgb="FFCCCCCC"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFB7E1CD"/>
+          <bgColor rgb="FFB7E1CD"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF4E1C3"/>
+          <bgColor rgb="FFF4E1C3"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFF4C7C3"/>
           <bgColor rgb="FFF4C7C3"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF4E1C3"/>
-          <bgColor rgb="FFF4E1C3"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFB7E1CD"/>
-          <bgColor rgb="FFB7E1CD"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFCCCCCC"/>
-          <bgColor rgb="FFCCCCCC"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -450,379 +422,804 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData/>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="9"/>
       <c r="B1" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="4">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="C2" s="4">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="D2" s="4">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="E2" s="4">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="F2" s="4">
-        <v>18.0</v>
+        <v>18</v>
       </c>
       <c r="G2" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="H2" s="4"/>
+        <v>18</v>
+      </c>
+      <c r="H2" s="9">
+        <v>18</v>
+      </c>
+      <c r="I2" s="9">
+        <v>18</v>
+      </c>
+      <c r="J2" s="9">
+        <v>18</v>
+      </c>
+      <c r="K2" s="9">
+        <v>18</v>
+      </c>
+      <c r="L2" s="9">
+        <v>18</v>
+      </c>
+      <c r="M2" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="4">
+        <v>18</v>
+      </c>
+      <c r="C3" s="4">
+        <v>18</v>
+      </c>
+      <c r="D3" s="4">
+        <v>18</v>
+      </c>
+      <c r="E3" s="4">
+        <v>18</v>
+      </c>
+      <c r="F3" s="4">
+        <v>18</v>
+      </c>
+      <c r="G3" s="4">
+        <v>18</v>
+      </c>
+      <c r="H3" s="9">
+        <v>18</v>
+      </c>
+      <c r="I3" s="9">
+        <v>18</v>
+      </c>
+      <c r="J3" s="9">
+        <v>18</v>
+      </c>
+      <c r="K3" s="9">
+        <v>18</v>
+      </c>
+      <c r="L3" s="9">
+        <v>18</v>
+      </c>
+      <c r="M3" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="4">
+        <v>18</v>
+      </c>
+      <c r="C4" s="4">
+        <v>18</v>
+      </c>
+      <c r="D4" s="4">
+        <v>18</v>
+      </c>
+      <c r="E4" s="4">
+        <v>18</v>
+      </c>
+      <c r="F4" s="4">
+        <v>18</v>
+      </c>
+      <c r="G4" s="4">
+        <v>18</v>
+      </c>
+      <c r="H4" s="9">
+        <v>18</v>
+      </c>
+      <c r="I4" s="9">
+        <v>18</v>
+      </c>
+      <c r="J4" s="9">
+        <v>18</v>
+      </c>
+      <c r="K4" s="9">
+        <v>18</v>
+      </c>
+      <c r="L4" s="9">
+        <v>18</v>
+      </c>
+      <c r="M4" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B5" s="4">
+        <v>18</v>
+      </c>
+      <c r="C5" s="4">
+        <v>18</v>
+      </c>
+      <c r="D5" s="4">
+        <v>18</v>
+      </c>
+      <c r="E5" s="4">
+        <v>18</v>
+      </c>
+      <c r="F5" s="4">
+        <v>18</v>
+      </c>
+      <c r="G5" s="4">
+        <v>18</v>
+      </c>
+      <c r="H5" s="9">
+        <v>18</v>
+      </c>
+      <c r="I5" s="9">
+        <v>18</v>
+      </c>
+      <c r="J5" s="9">
+        <v>18</v>
+      </c>
+      <c r="K5" s="9">
+        <v>18</v>
+      </c>
+      <c r="L5" s="9">
+        <v>18</v>
+      </c>
+      <c r="M5" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="4">
+        <v>18</v>
+      </c>
+      <c r="C6" s="4">
+        <v>18</v>
+      </c>
+      <c r="D6" s="4">
+        <v>18</v>
+      </c>
+      <c r="E6" s="4">
+        <v>18</v>
+      </c>
+      <c r="F6" s="4">
+        <v>18</v>
+      </c>
+      <c r="G6" s="4">
+        <v>18</v>
+      </c>
+      <c r="H6" s="9">
+        <v>18</v>
+      </c>
+      <c r="I6" s="9">
+        <v>18</v>
+      </c>
+      <c r="J6" s="9">
+        <v>18</v>
+      </c>
+      <c r="K6" s="9">
+        <v>18</v>
+      </c>
+      <c r="L6" s="9">
+        <v>18</v>
+      </c>
+      <c r="M6" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="4">
+        <v>18</v>
+      </c>
+      <c r="C7" s="4">
+        <v>18</v>
+      </c>
+      <c r="D7" s="4">
+        <v>18</v>
+      </c>
+      <c r="E7" s="4">
+        <v>18</v>
+      </c>
+      <c r="F7" s="4">
+        <v>18</v>
+      </c>
+      <c r="G7" s="4">
+        <v>18</v>
+      </c>
+      <c r="H7" s="9">
+        <v>18</v>
+      </c>
+      <c r="I7" s="9">
+        <v>18</v>
+      </c>
+      <c r="J7" s="9">
+        <v>18</v>
+      </c>
+      <c r="K7" s="9">
+        <v>18</v>
+      </c>
+      <c r="L7" s="9">
+        <v>18</v>
+      </c>
+      <c r="M7" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="4">
+        <v>18</v>
+      </c>
+      <c r="C8" s="4">
+        <v>18</v>
+      </c>
+      <c r="D8" s="4">
+        <v>18</v>
+      </c>
+      <c r="E8" s="4">
+        <v>18</v>
+      </c>
+      <c r="F8" s="4">
+        <v>18</v>
+      </c>
+      <c r="G8" s="4">
+        <v>18</v>
+      </c>
+      <c r="H8" s="9">
+        <v>18</v>
+      </c>
+      <c r="I8" s="9">
+        <v>18</v>
+      </c>
+      <c r="J8" s="9">
+        <v>18</v>
+      </c>
+      <c r="K8" s="9">
+        <v>18</v>
+      </c>
+      <c r="L8" s="9">
+        <v>18</v>
+      </c>
+      <c r="M8" s="9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="4">
+        <v>18</v>
+      </c>
+      <c r="C9" s="4">
+        <v>18</v>
+      </c>
+      <c r="D9" s="4">
+        <v>18</v>
+      </c>
+      <c r="E9" s="4">
+        <v>18</v>
+      </c>
+      <c r="F9" s="4">
+        <v>18</v>
+      </c>
+      <c r="G9" s="4">
+        <v>18</v>
+      </c>
+      <c r="H9" s="9">
+        <v>18</v>
+      </c>
+      <c r="I9" s="9">
+        <v>18</v>
+      </c>
+      <c r="J9" s="9">
+        <v>18</v>
+      </c>
+      <c r="K9" s="9">
+        <v>18</v>
+      </c>
+      <c r="L9" s="9">
+        <v>18</v>
+      </c>
+      <c r="M9" s="9">
+        <v>18</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:M22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+  <cols>
+    <col min="1" max="1" width="2.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.33203125" customWidth="1"/>
+    <col min="3" max="13" width="10.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="1"/>
+      <c r="B1" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="2">
+        <v>8</v>
+      </c>
+      <c r="J1" s="2">
+        <v>9</v>
+      </c>
+      <c r="K1" s="2">
+        <v>10</v>
+      </c>
+      <c r="L1" s="2">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
       <c r="K2" s="4"/>
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="C3" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="D3" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="E3" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="F3" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="G3" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="H3" s="4"/>
+      <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="C4" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="D4" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="E4" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="F4" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="G4" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="H4" s="4"/>
+      <c r="B4" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
       <c r="K4" s="4"/>
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="C5" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="D5" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="E5" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="F5" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="G5" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="H5" s="4"/>
+      <c r="B5" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
       <c r="K5" s="4"/>
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="C6" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="D6" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="E6" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="F6" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="G6" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="H6" s="4"/>
+      <c r="B6" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
       <c r="K6" s="4"/>
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="C7" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="D7" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="E7" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="F7" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="G7" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="H7" s="4"/>
+      <c r="B7" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="C8" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="D8" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="E8" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="F8" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="G8" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="H8" s="4"/>
+      <c r="B8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
       <c r="K8" s="4"/>
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="C9" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="D9" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="E9" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="F9" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="G9" s="4">
-        <v>18.0</v>
-      </c>
-      <c r="H9" s="4"/>
+      <c r="B9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>4</v>
+      </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
       <c r="K9" s="4"/>
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
+    <row r="22" spans="8:8" x14ac:dyDescent="0.2">
+      <c r="H22" s="4"/>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <conditionalFormatting sqref="D1:D9 B2:C9 E2:M9 H22">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="homozygous">
+      <formula>NOT(ISERROR(SEARCH(("homozygous"),(D1))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="heterozygous">
+      <formula>NOT(ISERROR(SEARCH(("heterozygous"),(D1))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="wildtype">
+      <formula>NOT(ISERROR(SEARCH(("wildtype"),(D1))))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="4" operator="containsText" text="unknown">
+      <formula>NOT(ISERROR(SEARCH(("unknown"),(D1))))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="2.25"/>
-    <col customWidth="1" min="2" max="2" width="9.38"/>
-    <col customWidth="1" min="3" max="13" width="10.5"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="2" max="13" width="8.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1"/>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" s="4"/>
       <c r="B1" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D1" s="3">
-        <v>3.0</v>
+        <v>2</v>
+      </c>
+      <c r="D1" s="2">
+        <v>3</v>
       </c>
       <c r="E1" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>3</v>
+      <c r="B2" s="3">
+        <v>0</v>
+      </c>
+      <c r="C2" s="7">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>0</v>
+      </c>
+      <c r="E2" s="3">
+        <v>0</v>
+      </c>
+      <c r="F2" s="6">
+        <v>2</v>
+      </c>
+      <c r="G2" s="6">
+        <v>2</v>
+      </c>
+      <c r="H2" s="3">
+        <v>0</v>
       </c>
       <c r="I2" s="4"/>
       <c r="J2" s="4"/>
@@ -830,30 +1227,30 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>3</v>
+      <c r="B3" s="3">
+        <v>0</v>
+      </c>
+      <c r="C3" s="7">
+        <v>0</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0</v>
       </c>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
@@ -861,30 +1258,30 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>3</v>
+      <c r="B4" s="3">
+        <v>0</v>
+      </c>
+      <c r="C4" s="7">
+        <v>0</v>
+      </c>
+      <c r="D4" s="3">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3">
+        <v>0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3">
+        <v>0</v>
       </c>
       <c r="I4" s="4"/>
       <c r="J4" s="4"/>
@@ -892,30 +1289,30 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>3</v>
+      <c r="B5" s="3">
+        <v>0</v>
+      </c>
+      <c r="C5" s="7">
+        <v>0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6">
+        <v>2</v>
+      </c>
+      <c r="G5" s="3">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
       </c>
       <c r="I5" s="4"/>
       <c r="J5" s="4"/>
@@ -923,30 +1320,30 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>4</v>
+      <c r="B6" s="3">
+        <v>0</v>
+      </c>
+      <c r="C6" s="7">
+        <v>0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>0</v>
+      </c>
+      <c r="F6" s="6">
+        <v>2</v>
+      </c>
+      <c r="G6" s="3">
+        <v>0</v>
+      </c>
+      <c r="H6" s="6">
+        <v>2</v>
       </c>
       <c r="I6" s="4"/>
       <c r="J6" s="4"/>
@@ -954,30 +1351,30 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>2</v>
+      <c r="B7" s="3">
+        <v>0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3">
+        <v>0</v>
+      </c>
+      <c r="F7" s="3">
+        <v>0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>2</v>
+      </c>
+      <c r="H7" s="3">
+        <v>0</v>
       </c>
       <c r="I7" s="4"/>
       <c r="J7" s="4"/>
@@ -985,30 +1382,30 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>3</v>
+      <c r="B8" s="3">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>0</v>
+      </c>
+      <c r="D8" s="6">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3">
+        <v>0</v>
       </c>
       <c r="I8" s="4"/>
       <c r="J8" s="4"/>
@@ -1016,360 +1413,30 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
-    </row>
-    <row r="22">
-      <c r="H22" s="4"/>
-    </row>
-  </sheetData>
-  <conditionalFormatting sqref="D1:D9 B2:C9 E2:M9 H22">
-    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="homozygous">
-      <formula>NOT(ISERROR(SEARCH(("homozygous"),(D1))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D9 B2:C9 E2:M9 H22">
-    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="heterozygous">
-      <formula>NOT(ISERROR(SEARCH(("heterozygous"),(D1))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D9 B2:C9 E2:M9 H22">
-    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="wildtype">
-      <formula>NOT(ISERROR(SEARCH(("wildtype"),(D1))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D1:D9 B2:C9 E2:M9 H22">
-    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="unknown">
-      <formula>NOT(ISERROR(SEARCH(("unknown"),(D1))))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
-  <cols>
-    <col customWidth="1" min="1" max="1" width="8.88"/>
-    <col customWidth="1" min="2" max="13" width="8.5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4"/>
-      <c r="B1" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="C1" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D1" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="E1" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="F1" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="G1" s="2">
-        <v>6.0</v>
-      </c>
-      <c r="H1" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="I1" s="2">
-        <v>8.0</v>
-      </c>
-      <c r="J1" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="K1" s="2">
-        <v>10.0</v>
-      </c>
-      <c r="L1" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="M1" s="2">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="D2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F2" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G2" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="H2" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C3" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="D3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H3" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="D4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C5" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="D5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F5" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C6" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F6" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="G6" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H6" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="E7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G7" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="H7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="C8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="D8" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="E8" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H8" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="B9" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="C9" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="D9" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="E9" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="F9" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="G9" s="3">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H9" s="6">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="I9" s="4"/>
       <c r="J9" s="4"/>
@@ -1388,60 +1455,60 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I1" s="8">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J1" s="8">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K1" s="8">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="L1" s="8">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="M1" s="8">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1472,7 +1539,7 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1503,7 +1570,7 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1534,7 +1601,7 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1565,7 +1632,7 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -1596,7 +1663,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -1627,7 +1694,7 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -1658,7 +1725,7 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -1690,57 +1757,58 @@
       <c r="M9" s="4"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -1781,7 +1849,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -1822,7 +1890,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -1863,7 +1931,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -1904,7 +1972,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -1945,7 +2013,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -1986,7 +2054,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -2027,7 +2095,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -2069,439 +2137,441 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col customWidth="1" min="2" max="13" width="9.0"/>
+    <col min="2" max="13" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="C2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="J2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="K2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L2" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="M2" s="2">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="C3" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H3" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I3" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="J3" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="K3" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L3" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="M3" s="2">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="C4" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D4" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F4" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G4" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H4" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I4" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="J4" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="K4" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L4" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="M4" s="2">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="C5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="J5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="K5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L5" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="M5" s="2">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="C6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="J6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="K6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L6" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="M6" s="2">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="C7" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D7" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F7" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G7" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H7" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I7" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="J7" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="K7" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L7" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="M7" s="2">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="C8" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D8" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F8" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G8" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H8" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I8" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="J8" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="K8" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L8" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="M8" s="2">
-        <v>14.0</v>
-      </c>
-    </row>
-    <row r="9">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="C9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="D9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="E9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="F9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="G9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="H9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="I9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="J9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="K9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="L9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
       <c r="M9" s="2">
-        <v>14.0</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2518,7 +2588,7 @@
       <c r="L2" s="4"/>
       <c r="M2" s="4"/>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2535,7 +2605,7 @@
       <c r="L3" s="4"/>
       <c r="M3" s="4"/>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -2552,7 +2622,7 @@
       <c r="L4" s="4"/>
       <c r="M4" s="4"/>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2569,7 +2639,7 @@
       <c r="L5" s="4"/>
       <c r="M5" s="4"/>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -2586,7 +2656,7 @@
       <c r="L6" s="4"/>
       <c r="M6" s="4"/>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2603,7 +2673,7 @@
       <c r="L7" s="4"/>
       <c r="M7" s="4"/>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -2620,7 +2690,7 @@
       <c r="L8" s="4"/>
       <c r="M8" s="4"/>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -2638,57 +2708,58 @@
       <c r="M9" s="4"/>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
@@ -2729,7 +2800,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
@@ -2770,7 +2841,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
@@ -2811,7 +2882,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
@@ -2852,7 +2923,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
@@ -2893,7 +2964,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
@@ -2934,7 +3005,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
@@ -2975,7 +3046,7 @@
         <v>28.5</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
@@ -3017,337 +3088,482 @@
       </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="9"/>
       <c r="B1" s="2">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C1" s="2">
-        <v>2.0</v>
+        <v>2</v>
       </c>
       <c r="D1" s="2">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="E1" s="2">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="F1" s="2">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="G1" s="2">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="H1" s="2">
-        <v>7.0</v>
+        <v>7</v>
       </c>
       <c r="I1" s="2">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="J1" s="2">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K1" s="2">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="L1" s="2">
-        <v>11.0</v>
+        <v>11</v>
       </c>
       <c r="M1" s="2">
-        <v>12.0</v>
-      </c>
-    </row>
-    <row r="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="10" t="str">
-        <f t="shared" ref="B2:G2" si="1">$A2 &amp; TEXT(B$1, "00")</f>
+        <f t="shared" ref="B2:M2" si="0">$A2 &amp; TEXT(B$1, "00")</f>
         <v>A01</v>
       </c>
       <c r="C2" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>A02</v>
       </c>
       <c r="D2" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>A03</v>
       </c>
       <c r="E2" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>A04</v>
       </c>
       <c r="F2" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>A05</v>
       </c>
       <c r="G2" s="10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>A06</v>
       </c>
-      <c r="H2" s="4"/>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4"/>
-      <c r="K2" s="4"/>
-      <c r="L2" s="4"/>
-      <c r="M2" s="4"/>
-    </row>
-    <row r="3">
+      <c r="H2" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>A07</v>
+      </c>
+      <c r="I2" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>A08</v>
+      </c>
+      <c r="J2" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>A09</v>
+      </c>
+      <c r="K2" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>A10</v>
+      </c>
+      <c r="L2" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>A11</v>
+      </c>
+      <c r="M2" s="10" t="str">
+        <f t="shared" si="0"/>
+        <v>A12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="10" t="str">
-        <f t="shared" ref="B3:G3" si="2">$A3 &amp; TEXT(B$1, "00")</f>
+        <f t="shared" ref="B3:M3" si="1">$A3 &amp; TEXT(B$1, "00")</f>
         <v>B01</v>
       </c>
       <c r="C3" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>B02</v>
       </c>
       <c r="D3" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>B03</v>
       </c>
       <c r="E3" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>B04</v>
       </c>
       <c r="F3" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>B05</v>
       </c>
       <c r="G3" s="10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>B06</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-    </row>
-    <row r="4">
+      <c r="H3" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>B07</v>
+      </c>
+      <c r="I3" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>B08</v>
+      </c>
+      <c r="J3" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>B09</v>
+      </c>
+      <c r="K3" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>B10</v>
+      </c>
+      <c r="L3" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>B11</v>
+      </c>
+      <c r="M3" s="10" t="str">
+        <f t="shared" si="1"/>
+        <v>B12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="10" t="str">
-        <f t="shared" ref="B4:G4" si="3">$A4 &amp; TEXT(B$1, "00")</f>
+        <f t="shared" ref="B4:M4" si="2">$A4 &amp; TEXT(B$1, "00")</f>
         <v>C01</v>
       </c>
       <c r="C4" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>C02</v>
       </c>
       <c r="D4" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>C03</v>
       </c>
       <c r="E4" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>C04</v>
       </c>
       <c r="F4" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>C05</v>
       </c>
       <c r="G4" s="10" t="str">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>C06</v>
       </c>
-      <c r="H4" s="4"/>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="4"/>
-      <c r="M4" s="4"/>
-    </row>
-    <row r="5">
+      <c r="H4" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>C07</v>
+      </c>
+      <c r="I4" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>C08</v>
+      </c>
+      <c r="J4" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>C09</v>
+      </c>
+      <c r="K4" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>C10</v>
+      </c>
+      <c r="L4" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>C11</v>
+      </c>
+      <c r="M4" s="10" t="str">
+        <f t="shared" si="2"/>
+        <v>C12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="10" t="str">
-        <f t="shared" ref="B5:G5" si="4">$A5 &amp; TEXT(B$1, "00")</f>
+        <f t="shared" ref="B5:M5" si="3">$A5 &amp; TEXT(B$1, "00")</f>
         <v>D01</v>
       </c>
       <c r="C5" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D02</v>
       </c>
       <c r="D5" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D03</v>
       </c>
       <c r="E5" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D04</v>
       </c>
       <c r="F5" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D05</v>
       </c>
       <c r="G5" s="10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="3"/>
         <v>D06</v>
       </c>
-      <c r="H5" s="4"/>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="4"/>
-      <c r="M5" s="4"/>
-    </row>
-    <row r="6">
+      <c r="H5" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>D07</v>
+      </c>
+      <c r="I5" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>D08</v>
+      </c>
+      <c r="J5" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>D09</v>
+      </c>
+      <c r="K5" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>D10</v>
+      </c>
+      <c r="L5" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>D11</v>
+      </c>
+      <c r="M5" s="10" t="str">
+        <f t="shared" si="3"/>
+        <v>D12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>8</v>
       </c>
       <c r="B6" s="10" t="str">
-        <f t="shared" ref="B6:G6" si="5">$A6 &amp; TEXT(B$1, "00")</f>
+        <f t="shared" ref="B6:M6" si="4">$A6 &amp; TEXT(B$1, "00")</f>
         <v>E01</v>
       </c>
       <c r="C6" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>E02</v>
       </c>
       <c r="D6" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>E03</v>
       </c>
       <c r="E6" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>E04</v>
       </c>
       <c r="F6" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>E05</v>
       </c>
       <c r="G6" s="10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>E06</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="4"/>
-      <c r="M6" s="4"/>
-    </row>
-    <row r="7">
+      <c r="H6" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>E07</v>
+      </c>
+      <c r="I6" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>E08</v>
+      </c>
+      <c r="J6" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>E09</v>
+      </c>
+      <c r="K6" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>E10</v>
+      </c>
+      <c r="L6" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>E11</v>
+      </c>
+      <c r="M6" s="10" t="str">
+        <f t="shared" si="4"/>
+        <v>E12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>9</v>
       </c>
       <c r="B7" s="10" t="str">
-        <f t="shared" ref="B7:G7" si="6">$A7 &amp; TEXT(B$1, "00")</f>
+        <f t="shared" ref="B7:M7" si="5">$A7 &amp; TEXT(B$1, "00")</f>
         <v>F01</v>
       </c>
       <c r="C7" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>F02</v>
       </c>
       <c r="D7" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>F03</v>
       </c>
       <c r="E7" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>F04</v>
       </c>
       <c r="F7" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>F05</v>
       </c>
       <c r="G7" s="10" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>F06</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="4"/>
-    </row>
-    <row r="8">
+      <c r="H7" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>F07</v>
+      </c>
+      <c r="I7" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>F08</v>
+      </c>
+      <c r="J7" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>F09</v>
+      </c>
+      <c r="K7" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>F10</v>
+      </c>
+      <c r="L7" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>F11</v>
+      </c>
+      <c r="M7" s="10" t="str">
+        <f t="shared" si="5"/>
+        <v>F12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="B8" s="10" t="str">
-        <f t="shared" ref="B8:G8" si="7">$A8 &amp; TEXT(B$1, "00")</f>
+        <f t="shared" ref="B8:M8" si="6">$A8 &amp; TEXT(B$1, "00")</f>
         <v>G01</v>
       </c>
       <c r="C8" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>G02</v>
       </c>
       <c r="D8" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>G03</v>
       </c>
       <c r="E8" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>G04</v>
       </c>
       <c r="F8" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>G05</v>
       </c>
       <c r="G8" s="10" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>G06</v>
       </c>
-      <c r="H8" s="4"/>
-      <c r="I8" s="4"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="4"/>
-      <c r="M8" s="4"/>
-    </row>
-    <row r="9">
+      <c r="H8" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>G07</v>
+      </c>
+      <c r="I8" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>G08</v>
+      </c>
+      <c r="J8" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>G09</v>
+      </c>
+      <c r="K8" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>G10</v>
+      </c>
+      <c r="L8" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>G11</v>
+      </c>
+      <c r="M8" s="10" t="str">
+        <f t="shared" si="6"/>
+        <v>G12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A9" s="4" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="10" t="str">
-        <f t="shared" ref="B9:G9" si="8">$A9 &amp; TEXT(B$1, "00")</f>
+        <f t="shared" ref="B9:M9" si="7">$A9 &amp; TEXT(B$1, "00")</f>
         <v>H01</v>
       </c>
       <c r="C9" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>H02</v>
       </c>
       <c r="D9" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>H03</v>
       </c>
       <c r="E9" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>H04</v>
       </c>
       <c r="F9" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>H05</v>
       </c>
       <c r="G9" s="10" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>H06</v>
       </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="4"/>
-      <c r="M9" s="4"/>
+      <c r="H9" s="10" t="str">
+        <f t="shared" si="7"/>
+        <v>H07</v>
+      </c>
+      <c r="I9" s="10" t="str">
+        <f t="shared" si="7"/>
+        <v>H08</v>
+      </c>
+      <c r="J9" s="10" t="str">
+        <f t="shared" si="7"/>
+        <v>H09</v>
+      </c>
+      <c r="K9" s="10" t="str">
+        <f t="shared" si="7"/>
+        <v>H10</v>
+      </c>
+      <c r="L9" s="10" t="str">
+        <f t="shared" si="7"/>
+        <v>H11</v>
+      </c>
+      <c r="M9" s="10" t="str">
+        <f t="shared" si="7"/>
+        <v>H12</v>
+      </c>
     </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/results/mcolon/20260607_sci_cilia_gene14_imaging_qc/source_plate_metadata_excels/20260414_b9d2_14hpf_plate02_well_metadata.xlsx
+++ b/results/mcolon/20260607_sci_cilia_gene14_imaging_qc/source_plate_metadata_excels/20260414_b9d2_14hpf_plate02_well_metadata.xlsx
@@ -17,6 +17,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="image_to_hash_map" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hash_plate_num" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="rt_block" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="collection_time_hpf" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -1425,6 +1426,402 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" t="n">
+        <v>1</v>
+      </c>
+      <c r="C1" t="n">
+        <v>2</v>
+      </c>
+      <c r="D1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1" t="n">
+        <v>4</v>
+      </c>
+      <c r="F1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H1" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1" t="n">
+        <v>8</v>
+      </c>
+      <c r="J1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1" t="n">
+        <v>10</v>
+      </c>
+      <c r="L1" t="n">
+        <v>11</v>
+      </c>
+      <c r="M1" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C2" t="n">
+        <v>14</v>
+      </c>
+      <c r="D2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E2" t="n">
+        <v>14</v>
+      </c>
+      <c r="F2" t="n">
+        <v>14</v>
+      </c>
+      <c r="G2" t="n">
+        <v>14</v>
+      </c>
+      <c r="H2" t="n">
+        <v>14</v>
+      </c>
+      <c r="I2" t="n">
+        <v>14</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14</v>
+      </c>
+      <c r="K2" t="n">
+        <v>14</v>
+      </c>
+      <c r="L2" t="n">
+        <v>14</v>
+      </c>
+      <c r="M2" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>14</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" t="n">
+        <v>14</v>
+      </c>
+      <c r="F3" t="n">
+        <v>14</v>
+      </c>
+      <c r="G3" t="n">
+        <v>14</v>
+      </c>
+      <c r="H3" t="n">
+        <v>14</v>
+      </c>
+      <c r="I3" t="n">
+        <v>14</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14</v>
+      </c>
+      <c r="K3" t="n">
+        <v>14</v>
+      </c>
+      <c r="L3" t="n">
+        <v>14</v>
+      </c>
+      <c r="M3" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>14</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" t="n">
+        <v>14</v>
+      </c>
+      <c r="E4" t="n">
+        <v>14</v>
+      </c>
+      <c r="F4" t="n">
+        <v>14</v>
+      </c>
+      <c r="G4" t="n">
+        <v>14</v>
+      </c>
+      <c r="H4" t="n">
+        <v>14</v>
+      </c>
+      <c r="I4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J4" t="n">
+        <v>14</v>
+      </c>
+      <c r="K4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M4" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>14</v>
+      </c>
+      <c r="C5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D5" t="n">
+        <v>14</v>
+      </c>
+      <c r="E5" t="n">
+        <v>14</v>
+      </c>
+      <c r="F5" t="n">
+        <v>14</v>
+      </c>
+      <c r="G5" t="n">
+        <v>14</v>
+      </c>
+      <c r="H5" t="n">
+        <v>14</v>
+      </c>
+      <c r="I5" t="n">
+        <v>14</v>
+      </c>
+      <c r="J5" t="n">
+        <v>14</v>
+      </c>
+      <c r="K5" t="n">
+        <v>14</v>
+      </c>
+      <c r="L5" t="n">
+        <v>14</v>
+      </c>
+      <c r="M5" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>14</v>
+      </c>
+      <c r="F6" t="n">
+        <v>14</v>
+      </c>
+      <c r="G6" t="n">
+        <v>14</v>
+      </c>
+      <c r="H6" t="n">
+        <v>14</v>
+      </c>
+      <c r="I6" t="n">
+        <v>14</v>
+      </c>
+      <c r="J6" t="n">
+        <v>14</v>
+      </c>
+      <c r="K6" t="n">
+        <v>14</v>
+      </c>
+      <c r="L6" t="n">
+        <v>14</v>
+      </c>
+      <c r="M6" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>14</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" t="n">
+        <v>14</v>
+      </c>
+      <c r="E7" t="n">
+        <v>14</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" t="n">
+        <v>14</v>
+      </c>
+      <c r="H7" t="n">
+        <v>14</v>
+      </c>
+      <c r="I7" t="n">
+        <v>14</v>
+      </c>
+      <c r="J7" t="n">
+        <v>14</v>
+      </c>
+      <c r="K7" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" t="n">
+        <v>14</v>
+      </c>
+      <c r="M7" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" t="n">
+        <v>14</v>
+      </c>
+      <c r="E8" t="n">
+        <v>14</v>
+      </c>
+      <c r="F8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G8" t="n">
+        <v>14</v>
+      </c>
+      <c r="H8" t="n">
+        <v>14</v>
+      </c>
+      <c r="I8" t="n">
+        <v>14</v>
+      </c>
+      <c r="J8" t="n">
+        <v>14</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" t="n">
+        <v>14</v>
+      </c>
+      <c r="M8" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>14</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="n">
+        <v>14</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14</v>
+      </c>
+      <c r="F9" t="n">
+        <v>14</v>
+      </c>
+      <c r="G9" t="n">
+        <v>14</v>
+      </c>
+      <c r="H9" t="n">
+        <v>14</v>
+      </c>
+      <c r="I9" t="n">
+        <v>14</v>
+      </c>
+      <c r="J9" t="n">
+        <v>14</v>
+      </c>
+      <c r="K9" t="n">
+        <v>14</v>
+      </c>
+      <c r="L9" t="n">
+        <v>14</v>
+      </c>
+      <c r="M9" t="n">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
